--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/AES-AircraftDesignToolbox-ASEN4138_Spr26_Feb23_Update/MAIN/Input Excel Sheets/Point Performance Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404CA4F6-FE07-7546-966A-CD486F87C1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629DD2D0-4D4F-FB4E-A59E-52BE3B53CD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="JB_V1" sheetId="10" r:id="rId2"/>
+    <sheet name="JB_{V1}" sheetId="10" r:id="rId2"/>
     <sheet name="C172" sheetId="3" r:id="rId3"/>
     <sheet name="B747" sheetId="6" r:id="rId4"/>
     <sheet name="TurboTilt" sheetId="8" r:id="rId5"/>
@@ -495,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -530,25 +530,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
+  <dxfs count="71">
     <dxf>
       <font>
         <b/>
@@ -2321,80 +2312,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
   <autoFilter ref="A1:K187" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55" tableBorderDxfId="54">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3048,12 +3039,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:I6">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J4 B7:J14">
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3116,49 +3107,41 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
       <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37">
+      <c r="A3" s="1"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10">
         <v>8000</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="10">
         <v>1.5</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="10">
         <v>30.414200000000001</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
       <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -3228,63 +3211,63 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="35" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="36">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="2">
         <v>8000</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="36">
         <v>1.5</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="2">
         <v>0.2</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="2">
         <v>0.1</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="2">
         <v>400</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="17"/>
@@ -3296,56 +3279,58 @@
       <c r="B8" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="41">
+      <c r="C9" s="38">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="38">
         <v>8000</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41">
+      <c r="E9" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="38">
         <v>1</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41">
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38">
         <v>0.1</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="38" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5664,18 +5649,18 @@
       <c r="K187" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 L2:XFD1048576 A10:K1048576 K6:K7 G2:K3 A9">
-    <cfRule type="expression" dxfId="13" priority="5">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 G2:K3 L2:XFD1048576 K6:K7 A9 A10:K1048576">
+    <cfRule type="expression" dxfId="12" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:J7">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:K5">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8577,17 +8562,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD3 J4:XFD4 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11489,17 +11474,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD4 C5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14353,22 +14338,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 F2:XFD2 B3:XFD3 J4:XFD4 B4:K11 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629DD2D0-4D4F-FB4E-A59E-52BE3B53CD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="4" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629DD2D0-4D4F-FB4E-A59E-52BE3B53CD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2390B4A6-E194-D340-87C0-1F32B53FE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="4" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
@@ -243,7 +243,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -491,11 +491,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -535,6 +570,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3130,16 +3185,16 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="10">
+      <c r="C3" s="46">
         <v>8000</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="46">
         <v>1.5</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="46">
         <v>30.414200000000001</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="46" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="17"/>
@@ -3194,7 +3249,7 @@
       <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="48" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="3">
@@ -3252,7 +3307,7 @@
       <c r="D7" s="2">
         <v>8000</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="47" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="36">
@@ -3267,7 +3322,7 @@
       <c r="I7" s="2">
         <v>400</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="50" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="17"/>
@@ -3322,11 +3377,15 @@
       <c r="F9" s="38">
         <v>1</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="H9" s="38">
+        <v>0</v>
+      </c>
+      <c r="I9" s="38">
+        <v>0</v>
+      </c>
       <c r="J9" s="38">
         <v>0.1</v>
       </c>
@@ -11556,44 +11615,44 @@
       <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="16"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3">
+      <c r="B3" s="14"/>
+      <c r="C3" s="43">
         <v>1</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="43">
         <v>5000</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="44">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="17"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
@@ -11602,44 +11661,44 @@
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
+      <c r="B5" s="14"/>
+      <c r="C5" s="43">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="43">
         <v>2</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="43">
         <v>160</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="17"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
@@ -11648,62 +11707,62 @@
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
+      <c r="B7" s="14"/>
+      <c r="C7" s="43">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="43">
         <v>22500</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="43">
         <v>0.3</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="43">
         <v>1</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="43">
         <v>0</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="43">
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="43">
         <v>0</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="43" t="s">
         <v>22</v>
       </c>
     </row>
@@ -11714,62 +11773,62 @@
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="40" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3">
+      <c r="B9" s="14"/>
+      <c r="C9" s="43">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="43">
         <v>20000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="43">
         <v>0.3</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="43">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="43">
         <v>1.67</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="43">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="43">
         <v>0</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="43" t="s">
         <v>28</v>
       </c>
     </row>
@@ -11780,62 +11839,62 @@
       <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="40" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="43">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="43">
         <v>5000</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="43">
         <v>0.3</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="43">
         <v>1.5</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="43">
         <v>0</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="43">
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="43">
         <v>0</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="43" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11846,103 +11905,103 @@
       <c r="B12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="45" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3">
+      <c r="B13" s="14"/>
+      <c r="C13" s="43">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="43">
         <v>15000</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="43">
         <v>0.4</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="43">
         <v>1</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="43">
         <v>0</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="43">
         <v>0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="43">
         <v>0</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="43" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="45"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="17"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="17"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="42"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2390B4A6-E194-D340-87C0-1F32B53FE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D18B5E-7D0B-A84C-8327-FCC58AB3EA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
-    <sheet name="JB_{V1}" sheetId="10" r:id="rId2"/>
+    <sheet name="JB_V1" sheetId="10" r:id="rId2"/>
     <sheet name="C172" sheetId="3" r:id="rId3"/>
     <sheet name="B747" sheetId="6" r:id="rId4"/>
     <sheet name="TurboTilt" sheetId="8" r:id="rId5"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D18B5E-7D0B-A84C-8327-FCC58AB3EA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183CC8A0-A5C2-924D-95CC-299F83526B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>43</v>
@@ -3317,7 +3317,7 @@
         <v>0.2</v>
       </c>
       <c r="H7" s="2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
         <v>400</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="38">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="38" t="s">
         <v>44</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183CC8A0-A5C2-924D-95CC-299F83526B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE8A906-A9B3-B74A-938F-EBD3FA4668AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -530,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -571,12 +571,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3185,16 +3181,16 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="46">
+      <c r="C3" s="42">
         <v>8000</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="42">
         <v>1.5</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="42">
         <v>30.414200000000001</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="42" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="17"/>
@@ -3249,7 +3245,7 @@
       <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="44" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="3">
@@ -3307,7 +3303,7 @@
       <c r="D7" s="2">
         <v>8000</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="43" t="s">
         <v>32</v>
       </c>
       <c r="F7" s="36">
@@ -3322,7 +3318,7 @@
       <c r="I7" s="2">
         <v>400</v>
       </c>
-      <c r="J7" s="50" t="s">
+      <c r="J7" s="46" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="17"/>
@@ -3375,9 +3371,9 @@
         <v>0.1</v>
       </c>
       <c r="F9" s="38">
-        <v>1</v>
-      </c>
-      <c r="G9" s="49" t="s">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G9" s="45" t="s">
         <v>32</v>
       </c>
       <c r="H9" s="38">
@@ -11615,44 +11611,37 @@
       <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="14"/>
-      <c r="C3" s="43">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="2">
         <v>5000</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="36">
         <v>10</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
@@ -11661,44 +11650,34 @@
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="14"/>
-      <c r="C5" s="43">
+      <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="2">
         <v>160</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
@@ -11707,62 +11686,62 @@
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="43" t="s">
+      <c r="K6" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="14"/>
-      <c r="C7" s="43">
+      <c r="C7" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="2">
         <v>22500</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="2">
         <v>0.3</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="s">
+      <c r="K7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -11773,62 +11752,62 @@
       <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="14"/>
-      <c r="C9" s="43">
+      <c r="C9" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="2">
         <v>20000</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="2">
         <v>0.3</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="2">
         <v>1.67</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="s">
+      <c r="K9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -11839,62 +11818,62 @@
       <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="40" t="s">
+      <c r="J10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="40" t="s">
+      <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="14"/>
-      <c r="C11" s="43">
+      <c r="C11" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="2">
         <v>5000</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="2">
         <v>0.3</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="2">
         <v>1.5</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="2">
         <v>0</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="2">
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="s">
+      <c r="K11" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11905,103 +11884,94 @@
       <c r="B12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="45" t="s">
+      <c r="I12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="45" t="s">
+      <c r="J12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="14"/>
-      <c r="C13" s="43">
+      <c r="C13" s="2">
         <v>0.85199999999999998</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="2">
         <v>15000</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="2">
         <v>0.4</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="2">
         <v>0</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="2">
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="s">
+      <c r="K13" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="14"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="3"/>
       <c r="C16" s="39"/>
-      <c r="D16" s="40"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
       <c r="G16" s="39"/>
       <c r="H16" s="39"/>
-      <c r="I16" s="41"/>
+      <c r="I16" s="40"/>
       <c r="J16" s="39"/>
-      <c r="K16" s="42"/>
+      <c r="K16" s="41"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE8A906-A9B3-B74A-938F-EBD3FA4668AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72912F9-F61D-894A-8000-CE7E88EE68FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -3185,7 +3185,7 @@
         <v>8000</v>
       </c>
       <c r="D3" s="42">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E3" s="42">
         <v>30.414200000000001</v>
@@ -3307,7 +3307,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="36">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
         <v>0.2</v>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72912F9-F61D-894A-8000-CE7E88EE68FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CBA85C-FB72-5546-9662-DFC351658257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="47">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -171,10 +171,16 @@
     <t>VTOL Takeoff</t>
   </si>
   <si>
-    <t>Max Mach (Max Speed)</t>
+    <t>Objective Max Loading Factor</t>
   </si>
   <si>
-    <t>Max Sustained Turn</t>
+    <t>Objective Max Mach</t>
+  </si>
+  <si>
+    <t>Objecrtive Stall Velocity</t>
+  </si>
+  <si>
+    <t>Objective Takeoff Distance</t>
   </si>
 </sst>
 </file>
@@ -3191,7 +3197,7 @@
         <v>30.414200000000001</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K3" s="17"/>
     </row>
@@ -3258,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3319,7 +3325,7 @@
         <v>400</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K7" s="17"/>
     </row>
@@ -3386,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CBA85C-FB72-5546-9662-DFC351658257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2933FC2-409C-1D47-B89F-B76B53DE1B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>VTOL Takeoff</t>
-  </si>
-  <si>
-    <t>Objective Max Loading Factor</t>
   </si>
   <si>
     <t>Objective Max Mach</t>
@@ -3197,7 +3194,7 @@
         <v>30.414200000000001</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K3" s="17"/>
     </row>
@@ -3264,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3325,75 +3322,35 @@
         <v>400</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="33">
-        <v>4</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="37" t="s">
-        <v>19</v>
-      </c>
+      <c r="A8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="38">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="D9" s="38">
-        <v>8000</v>
-      </c>
-      <c r="E9" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="38">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="38">
-        <v>0</v>
-      </c>
-      <c r="I9" s="38">
-        <v>0</v>
-      </c>
-      <c r="J9" s="38">
-        <v>0</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>43</v>
-      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -5710,7 +5667,7 @@
       <c r="K187" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 G2:K3 L2:XFD1048576 K6:K7 A9 A10:K1048576">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 G2:K3 L2:XFD1048576 K6:K7 A9 A16:K1048576 A15:B15 D15:K15 A10:K14">
     <cfRule type="expression" dxfId="12" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/ZW_Snr_Proj_Requirements_Input.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zackwoj/Documents/MATLAB/26-27/Fall/Aircraft Design/Team06_SeniorProj/USE_THIS_DESIGN_CODE/Input Excel Sheets/Point Performance Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2933FC2-409C-1D47-B89F-B76B53DE1B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E98BD27-F3A7-3A44-9C3A-E805AC24A85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="1" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" activeTab="2" xr2:uid="{AC12A90C-16A5-0547-A6DB-57534C200D25}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates" sheetId="2" r:id="rId1"/>
     <sheet name="JB_V1" sheetId="10" r:id="rId2"/>
-    <sheet name="C172" sheetId="3" r:id="rId3"/>
-    <sheet name="B747" sheetId="6" r:id="rId4"/>
-    <sheet name="TurboTilt" sheetId="8" r:id="rId5"/>
+    <sheet name="JB_Verification" sheetId="11" r:id="rId3"/>
+    <sheet name="C172" sheetId="3" r:id="rId4"/>
+    <sheet name="B747" sheetId="6" r:id="rId5"/>
+    <sheet name="TurboTilt" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="49">
   <si>
     <t>Coef Friction</t>
   </si>
@@ -179,6 +180,15 @@
   <si>
     <t>Objective Takeoff Distance</t>
   </si>
+  <si>
+    <t>35 mph Stall Velo</t>
+  </si>
+  <si>
+    <t>400 ft landing distance</t>
+  </si>
+  <si>
+    <t>400 ft takeoff distance</t>
+  </si>
 </sst>
 </file>
 
@@ -246,7 +256,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -529,11 +539,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -589,11 +627,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="89">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2352,6 +2420,423 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2366,80 +2851,100 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EA520BC-547E-FB42-9345-C10BE812E714}" name="Table326" displayName="Table326" ref="A1:K187" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87" tableBorderDxfId="86">
   <autoFilter ref="A1:K187" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{4E873125-B430-DF47-97E8-8718CA85A22C}" name="Requirement #" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{F52F1F07-B543-0B47-8053-E34E2BA8895A}" name="Requirement Type" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{FE328122-9A74-7A4B-B57D-BF029EDE1844}" name="Input 1" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{418B51CA-8898-B442-BEE4-8304BF1CD6C0}" name="Input 2" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{A456BF20-760C-3A48-A400-7558B03C7A73}" name="Input 3" dataDxfId="81"/>
+    <tableColumn id="6" xr3:uid="{C9B3AF7B-40A5-7A4B-954F-08C72C3E8D95}" name="Input 4" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{A6995574-966C-AA49-8F26-8C85A4851905}" name="Input 5" dataDxfId="79"/>
+    <tableColumn id="8" xr3:uid="{976E4B5C-CC56-E948-9B3D-4F36230C9950}" name="Input 6" dataDxfId="78"/>
+    <tableColumn id="9" xr3:uid="{D10F34FA-7944-934F-B09F-BFE9ED3EFBC2}" name="Input 7" dataDxfId="77"/>
+    <tableColumn id="10" xr3:uid="{C3452EA2-25EF-274F-BAF6-358D378B7C56}" name="Input 8" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{95D5D1CA-CE7A-B245-9964-B82D986B951F}" name="Input 9" dataDxfId="75"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55" tableBorderDxfId="54">
-  <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{77861601-4455-7245-A43A-6F8728C9A9FA}" name="Table3264" displayName="Table3264" ref="A1:K189" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+  <autoFilter ref="A1:K189" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{C74726FD-6A14-2A4B-83BA-FBFF632779EA}" name="Requirement #" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{7EF58860-813F-044F-B55E-477B5212A541}" name="Requirement Type" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{A1AD929D-6EBC-BC4B-A1CB-DA17E71EDBBE}" name="Input 1" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C379CFB7-9C5D-8A48-9E0A-43FFDF0F09F1}" name="Input 2" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{02BB6418-CCAD-B04D-BD8B-1C6B1BC56F8C}" name="Input 3" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{5EBAB405-C56C-A946-A053-DCAE94F2AA3B}" name="Input 4" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{72E64B4E-E593-3247-9355-F63A60B7BBCC}" name="Input 5" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{F385EF4E-687E-224A-AFB9-C5E32AEEF500}" name="Input 6" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{B99F34C2-56F8-8E45-AD7F-51204DB0002D}" name="Input 7" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{4A43A236-23D5-C34A-9360-409BB4B776D8}" name="Input 8" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{727827F2-9B89-E94C-B43F-AC1EBA1BFFB2}" name="Input 9" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41" tableBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16D9459C-59A6-BF4A-A7B6-FBED165ADCA1}" name="Table32" displayName="Table32" ref="A1:K200" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73" tableBorderDxfId="72">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{05E785CD-BA1A-0741-A8C1-F103F004A333}" name="Requirement #" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{65ED0781-559E-BB4A-95BC-C03BEB6F0FD3}" name="Requirement Type" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{A5BC6781-8D14-CA4A-8CC8-894BC40040CF}" name="Input 1" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{426A3784-CB12-634C-B28C-1912BBEDA639}" name="Input 2" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{6CB1F183-1B01-524E-A8C5-EFDF25C9EC6E}" name="Input 3" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{018A88FF-960F-EE4D-AA98-1781DA96E06D}" name="Input 4" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{DA0F16CA-219B-2C46-8309-C7D52FE83C6B}" name="Input 5" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{9E89BB34-08B2-3641-902A-0475DC098911}" name="Input 6" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{BC7719A6-3F10-F04A-ADE2-39707C03237F}" name="Input 7" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{B83931B8-07AE-B044-9121-BD48FE4CFC72}" name="Input 8" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{A1FD63F7-D5E1-E742-9C9A-DB3936B5DD1F}" name="Input 9" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E9925791-6FE9-D24F-854A-AA3A87983F7A}" name="Table323" displayName="Table323" ref="A1:K200" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59" tableBorderDxfId="58">
   <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{79B11DD2-72B5-A244-9BA2-010F65DA0C71}" name="Requirement #" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{A92F991A-F478-DF49-9573-45217E106A85}" name="Requirement Type" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{426F7ACD-E846-6B45-8580-16C9BC5B34B5}" name="Input 1" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{D8AF62F2-8523-1145-A81E-A1364337806B}" name="Input 2" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{84BDE2D1-2330-CF41-AEE0-9F5842569747}" name="Input 3" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{FE5DDCDE-FABD-E946-863B-C6BB28097755}" name="Input 4" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{18A756AC-E9D0-6E49-A4DE-24B7F35F91C5}" name="Input 5" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{21B200F8-22B2-0648-80FC-4820DECF0D5B}" name="Input 6" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{CB23FB5A-7884-AD4D-B71C-6E6EDDBF2886}" name="Input 7" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{40228DA8-61D6-1647-A4A3-EDA3C2FFFECB}" name="Input 8" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{F6825A5F-3D00-6E44-B99F-13492A664278}" name="Input 9" dataDxfId="47"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0A78BEFF-89A3-F74D-8EB9-3ED264AED86C}" name="Table325" displayName="Table325" ref="A1:K200" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+  <autoFilter ref="A1:K200" xr:uid="{E9D8E600-FE9F-5C45-8634-0D6DD0E667E3}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{8E8452FB-D4CF-024D-BED9-0263227800CC}" name="Requirement #" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{09D97C96-66EE-464A-9495-9BC41CC97CDD}" name="Requirement Type" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{C5833324-76B6-ED46-ABE8-8C26CB8A929F}" name="Input 1" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{516580E8-43B2-A94E-BF87-D7CABADDFD20}" name="Input 2" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{D7E38409-68A4-2348-A254-F99A28B3D6AA}" name="Input 3" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{0DA05089-DF15-DA46-B1A0-0DE642F3AB90}" name="Input 4" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{2CCEF327-B870-1046-92B1-14A71A3CA901}" name="Input 5" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{C8111718-8D74-F54C-A527-0FADE5F57B9B}" name="Input 6" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{33F897C6-7671-8849-BBAE-D1E7CF3CB1B0}" name="Input 7" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{91964FF9-90FD-8646-9211-E7DF64E561A3}" name="Input 8" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{C84CDF7D-F0F0-D348-8A57-B96AD3A17DB7}" name="Input 9" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3093,12 +3598,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:I6">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J4 B7:J14">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5667,18 +6172,18 @@
       <c r="K187" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:B1 D1:XFD1 G2:K3 L2:XFD1048576 K6:K7 A9 A16:K1048576 A15:B15 D15:K15 A10:K14">
-    <cfRule type="expression" dxfId="12" priority="5">
+  <conditionalFormatting sqref="A1:B1 D1:XFD1 G2:K3 L2:XFD1048576 K6:K7 A9 A10:K14 A15:B15 D15:K15 A16:K1048576">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6:J7">
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:K5">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5690,6 +6195,2652 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805A2B36-1661-4F4B-9766-59992C87FFB0}">
+  <dimension ref="A1:K189"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="40.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.5" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="49"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="38">
+        <v>1</v>
+      </c>
+      <c r="D3" s="38">
+        <v>8000</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="38">
+        <v>2</v>
+      </c>
+      <c r="G3" s="38">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H3" s="38">
+        <v>1.5E-3</v>
+      </c>
+      <c r="I3" s="38">
+        <v>400</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" s="50"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="42">
+        <v>8000</v>
+      </c>
+      <c r="D5" s="42">
+        <v>2</v>
+      </c>
+      <c r="E5" s="42">
+        <v>30.414200000000001</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="35"/>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.5E-3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>400</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="46"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="4"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="4"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="4"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="4"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="4"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="4"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="4"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="4"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="4"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="4"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="4"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="4"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="4"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="4"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="4"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="4"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="4"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="4"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="4"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="4"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="4"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="4"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="4"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="4"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="4"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="4"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="17"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="4"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="17"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="4"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="17"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="4"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="17"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="4"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="4"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="4"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="4"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="4"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="4"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="4"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="17"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="4"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="4"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="4"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="4"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="4"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="17"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="4"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="4"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="17"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="4"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="17"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="4"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="17"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="4"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="17"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="4"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="17"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="4"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="17"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="4"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="14"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="17"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="4"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="17"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="4"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="17"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="4"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="14"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="17"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="4"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="17"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="4"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="14"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="17"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="4"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="14"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="17"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="4"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="14"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="17"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="4"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="14"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="17"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="4"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="14"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="17"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="4"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="14"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="17"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="4"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="17"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="4"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="17"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="4"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="17"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="4"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="17"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="4"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="14"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="17"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="4"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="14"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="17"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="4"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="14"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="17"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="4"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="14"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="17"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="4"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="14"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="17"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="14"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="17"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="4"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="14"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="17"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="4"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="14"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="17"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="4"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="14"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="17"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="14"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="17"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="14"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="17"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="14"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="17"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="4"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="14"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="17"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="4"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="14"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="17"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="4"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="14"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="17"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="4"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="14"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="17"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="4"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="17"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="4"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="14"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="17"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="4"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="14"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="17"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="4"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="14"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="17"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="4"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="14"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="17"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="4"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="14"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="17"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="4"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="14"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="17"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="4"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="14"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="17"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="4"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="14"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="17"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="4"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="14"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="17"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="4"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="14"/>
+      <c r="J148" s="3"/>
+      <c r="K148" s="17"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="14"/>
+      <c r="J149" s="3"/>
+      <c r="K149" s="17"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="4"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="14"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="17"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="4"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="14"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="17"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="4"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="14"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="17"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="4"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="14"/>
+      <c r="J153" s="3"/>
+      <c r="K153" s="17"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="4"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="14"/>
+      <c r="J154" s="3"/>
+      <c r="K154" s="17"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="4"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="14"/>
+      <c r="J155" s="3"/>
+      <c r="K155" s="17"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="4"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="14"/>
+      <c r="J156" s="3"/>
+      <c r="K156" s="17"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="4"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="14"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="17"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="4"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="14"/>
+      <c r="J158" s="3"/>
+      <c r="K158" s="17"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="14"/>
+      <c r="J159" s="3"/>
+      <c r="K159" s="17"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="4"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="14"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="17"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="4"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="14"/>
+      <c r="J161" s="3"/>
+      <c r="K161" s="17"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="4"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="14"/>
+      <c r="J162" s="3"/>
+      <c r="K162" s="17"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="4"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="14"/>
+      <c r="J163" s="3"/>
+      <c r="K163" s="17"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="4"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="14"/>
+      <c r="J164" s="3"/>
+      <c r="K164" s="17"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="4"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="17"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="4"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="14"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="17"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="14"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="17"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" s="4"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="14"/>
+      <c r="J168" s="3"/>
+      <c r="K168" s="17"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="4"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="14"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="17"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="4"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="14"/>
+      <c r="J170" s="3"/>
+      <c r="K170" s="17"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="14"/>
+      <c r="J171" s="3"/>
+      <c r="K171" s="17"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="4"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="14"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="17"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="4"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="14"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="17"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="4"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="14"/>
+      <c r="J174" s="3"/>
+      <c r="K174" s="17"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="4"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="14"/>
+      <c r="J175" s="3"/>
+      <c r="K175" s="17"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="4"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="14"/>
+      <c r="J176" s="3"/>
+      <c r="K176" s="17"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="4"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="14"/>
+      <c r="J177" s="3"/>
+      <c r="K177" s="17"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="4"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="14"/>
+      <c r="J178" s="3"/>
+      <c r="K178" s="17"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="4"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="14"/>
+      <c r="J179" s="3"/>
+      <c r="K179" s="17"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="4"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="14"/>
+      <c r="J180" s="3"/>
+      <c r="K180" s="17"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="4"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="14"/>
+      <c r="J181" s="3"/>
+      <c r="K181" s="17"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="4"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="14"/>
+      <c r="J182" s="3"/>
+      <c r="K182" s="17"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" s="4"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="14"/>
+      <c r="J183" s="3"/>
+      <c r="K183" s="17"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="4"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="14"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="17"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="4"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="14"/>
+      <c r="J185" s="3"/>
+      <c r="K185" s="17"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="4"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="14"/>
+      <c r="J186" s="3"/>
+      <c r="K186" s="17"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="4"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="14"/>
+      <c r="J187" s="3"/>
+      <c r="K187" s="17"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="4"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="14"/>
+      <c r="J188" s="3"/>
+      <c r="K188" s="17"/>
+    </row>
+    <row r="189" spans="1:11" ht="19" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="12"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
+      <c r="I189" s="15"/>
+      <c r="J189" s="3"/>
+      <c r="K189" s="18"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D1:XFD1 G4:K5 L2:XFD1048576 K8:K9 A11 A12:K16 A17:B17 D17:K17 A18:K1048576 A1:B1 A2:A3">
+    <cfRule type="expression" dxfId="13" priority="4">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J9">
+    <cfRule type="expression" dxfId="12" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:K7">
+    <cfRule type="expression" dxfId="11" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:I9">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B580E99C-C8B6-6643-837C-0DA39C79301D}">
   <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
@@ -8580,17 +11731,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD3 J4:XFD4 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8601,7 +11752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D249185F-EB86-B542-8B5B-7CCC7BD8C54D}">
   <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
@@ -11492,17 +14643,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 B2:XFD4 C5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11513,7 +14664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C1AABD-3C43-6F40-828B-6CE36050BFAD}">
   <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
@@ -14330,22 +17481,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1 D1:XFD1 F2:XFD2 B3:XFD3 J4:XFD4 B4:K11 K5:XFD5 B6:XFD13 L14:XFD14 F15:XFD21 B16:E21 A22:XFD1048576">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:I5">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
